--- a/react-demo/public/template.xlsx
+++ b/react-demo/public/template.xlsx
@@ -16,9 +16,11 @@
     <definedName name="buildingArea">评估明细表!$B$2</definedName>
     <definedName name="daf" localSheetId="0">评估明细表!$F$3</definedName>
     <definedName name="haha">评估明细表!$F$2</definedName>
+    <definedName name="hanzi">评估明细表!$C$5</definedName>
     <definedName name="test">评估明细表!$E$2</definedName>
     <definedName name="totalValuationPrice">评估明细表!$D$2</definedName>
     <definedName name="valuationPrice">评估明细表!$C$2</definedName>
+    <definedName name="wenben">评估明细表!$B$5</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
@@ -429,13 +431,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="4" width="21.875" customWidth="1"/>
+    <col min="6" max="6" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -452,7 +455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -470,34 +473,59 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="B3" s="1">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1">
+        <v>5000</v>
+      </c>
+      <c r="D3" s="1">
+        <f>ROUND(C3*B3/10000,2)</f>
+        <v>5</v>
+      </c>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+      <c r="B4" s="1">
+        <v>245</v>
+      </c>
+      <c r="C4" s="1">
+        <v>254</v>
+      </c>
+      <c r="D4" s="1">
+        <f>C4+B4</f>
+        <v>499</v>
+      </c>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="1">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1">
+        <v>150</v>
+      </c>
+      <c r="D5" s="1">
+        <f>hanzi+wenben</f>
+        <v>160</v>
+      </c>
       <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F5" t="str">
+        <f>IF(D5&gt;100,"大于100","小于等于100")</f>
+        <v>大于100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -506,7 +534,7 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -515,7 +543,7 @@
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -524,7 +552,7 @@
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -533,7 +561,7 @@
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -542,7 +570,7 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -551,7 +579,7 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -560,7 +588,7 @@
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -569,7 +597,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -578,7 +606,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -587,7 +615,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>15</v>
       </c>

--- a/react-demo/public/template.xlsx
+++ b/react-demo/public/template.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -55,6 +55,9 @@
   <si>
     <t>备注无</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我</t>
   </si>
 </sst>
 </file>
@@ -487,7 +490,9 @@
         <f>ROUND(C3*B3/10000,2)</f>
         <v>5</v>
       </c>
-      <c r="E3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="1">

--- a/react-demo/public/template.xlsx
+++ b/react-demo/public/template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="评估明细表" sheetId="1" r:id="rId1"/>
@@ -697,40 +697,57 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K11"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A1">
+        <v>2</v>
+      </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="C1">
+        <v>54</v>
+      </c>
+      <c r="D1">
+        <v>542</v>
+      </c>
+      <c r="I1">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="I4">
         <v>254245</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="K5">
         <v>24524</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="I8">
         <v>2452452</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="G9">
         <v>2452452</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="G11">
         <v>1425425</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C20">
+        <v>578</v>
       </c>
     </row>
   </sheetData>
@@ -741,9 +758,25 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="B1:E12"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B1">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D2">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="E12">
+        <v>578</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -751,9 +784,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="E2:F11"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="F2">
+        <v>578578</v>
+      </c>
+    </row>
+    <row r="11" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E11">
+        <v>578578</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/react-demo/public/template.xlsx
+++ b/react-demo/public/template.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8667EC08-BA2F-4A6A-B519-3C7BACD05EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
+    <workbookView xWindow="5475" yWindow="1695" windowWidth="29565" windowHeight="18060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="评估明细表" sheetId="1" r:id="rId1"/>
@@ -22,12 +23,23 @@
     <definedName name="valuationPrice">评估明细表!$C$2</definedName>
     <definedName name="wenben">评估明细表!$B$5</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -59,11 +71,15 @@
   <si>
     <t>我</t>
   </si>
+  <si>
+    <t>求和</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -87,12 +103,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -130,7 +152,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -143,14 +165,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -188,7 +213,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -260,7 +285,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -433,7 +458,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -454,7 +479,7 @@
       <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -474,6 +499,10 @@
       </c>
       <c r="E2" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="F2">
+        <f>D11</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
@@ -543,7 +572,9 @@
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="1"/>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -552,7 +583,9 @@
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1">
+        <v>60</v>
+      </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -561,7 +594,9 @@
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="1">
+        <v>70</v>
+      </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -570,7 +605,9 @@
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="1">
+        <v>50</v>
+      </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -579,7 +616,9 @@
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="1"/>
+      <c r="B11" s="1">
+        <v>80</v>
+      </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -588,7 +627,10 @@
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="1"/>
+      <c r="B12" s="3">
+        <f>SUM(B8:B11)</f>
+        <v>260</v>
+      </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -686,7 +728,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"你,我,她"</formula1>
     </dataValidation>
   </dataValidations>
@@ -696,7 +738,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -757,7 +799,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:E12"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
@@ -783,7 +825,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="E2:F11"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>

--- a/react-demo/public/template.xlsx
+++ b/react-demo/public/template.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8667EC08-BA2F-4A6A-B519-3C7BACD05EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5475" yWindow="1695" windowWidth="29565" windowHeight="18060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5475" yWindow="1695" windowWidth="29565" windowHeight="18060"/>
   </bookViews>
   <sheets>
     <sheet name="评估明细表" sheetId="1" r:id="rId1"/>
@@ -15,6 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="buildingArea">评估明细表!$B$2</definedName>
+    <definedName name="Choose">评估明细表!$E$3</definedName>
     <definedName name="daf" localSheetId="0">评估明细表!$F$3</definedName>
     <definedName name="haha">评估明细表!$F$2</definedName>
     <definedName name="hanzi">评估明细表!$C$5</definedName>
@@ -23,7 +23,7 @@
     <definedName name="valuationPrice">评估明细表!$C$2</definedName>
     <definedName name="wenben">评估明细表!$B$5</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -173,9 +173,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -213,7 +213,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -285,7 +285,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -458,7 +458,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -501,8 +501,8 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <f>D11</f>
-        <v>0</v>
+        <f>totalValuationPrice</f>
+        <v>12.5</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
@@ -728,7 +728,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3">
       <formula1>"你,我,她"</formula1>
     </dataValidation>
   </dataValidations>
@@ -738,7 +738,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -799,7 +799,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:E12"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
@@ -825,7 +825,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="E2:F11"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>

--- a/react-demo/public/template.xlsx
+++ b/react-demo/public/template.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD6E7F8-19A8-4A48-811B-85B73327FE04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5475" yWindow="1695" windowWidth="29565" windowHeight="18060"/>
+    <workbookView xWindow="7005" yWindow="4485" windowWidth="29565" windowHeight="18060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="评估明细表" sheetId="1" r:id="rId1"/>
@@ -13,17 +14,19 @@
     <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="buildingArea">评估明细表!$B$2</definedName>
-    <definedName name="Choose">评估明细表!$E$3</definedName>
-    <definedName name="daf" localSheetId="0">评估明细表!$F$3</definedName>
-    <definedName name="haha">评估明细表!$F$2</definedName>
-    <definedName name="hanzi">评估明细表!$C$5</definedName>
-    <definedName name="test">评估明细表!$E$2</definedName>
-    <definedName name="totalValuationPrice">评估明细表!$D$2</definedName>
-    <definedName name="valuationPrice">评估明细表!$C$2</definedName>
-    <definedName name="wenben">评估明细表!$B$5</definedName>
+    <definedName name="buildingArea">评估明细表!$C$2</definedName>
+    <definedName name="Choose">评估明细表!$F$3</definedName>
+    <definedName name="daf" localSheetId="0">评估明细表!$G$3</definedName>
+    <definedName name="haha">评估明细表!$G$2</definedName>
+    <definedName name="hanzi">评估明细表!$D$5</definedName>
+    <definedName name="location">评估明细表!$B$2</definedName>
+    <definedName name="reportID">评估明细表!$A$2</definedName>
+    <definedName name="test">评估明细表!$F$2</definedName>
+    <definedName name="totalValuationPrice">评估明细表!$E$2</definedName>
+    <definedName name="valuationPrice">评估明细表!$D$2</definedName>
+    <definedName name="wenben">评估明细表!$C$5</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -73,13 +76,21 @@
   </si>
   <si>
     <t>求和</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坐落</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>的说法</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -173,9 +184,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -213,7 +224,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -285,7 +296,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -458,108 +469,117 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="4" width="21.875" customWidth="1"/>
-    <col min="6" max="6" width="11.625" customWidth="1"/>
+    <col min="1" max="5" width="21.875" customWidth="1"/>
+    <col min="7" max="7" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1">
         <v>25</v>
       </c>
-      <c r="C2" s="1">
+      <c r="D2" s="1">
         <v>5000</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
         <f>ROUND(valuationPrice*buildingArea/10000,2)</f>
         <v>12.5</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <f>totalValuationPrice</f>
         <v>12.5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1">
         <v>10</v>
       </c>
-      <c r="C3" s="1">
+      <c r="D3" s="1">
         <v>5000</v>
       </c>
-      <c r="D3" s="1">
-        <f>ROUND(C3*B3/10000,2)</f>
+      <c r="E3" s="1">
+        <f>ROUND(D3*C3/10000,2)</f>
         <v>5</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1">
         <v>245</v>
       </c>
-      <c r="C4" s="1">
+      <c r="D4" s="1">
         <v>254</v>
       </c>
-      <c r="D4" s="1">
-        <f>C4+B4</f>
+      <c r="E4" s="1">
+        <f>D4+C4</f>
         <v>499</v>
       </c>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1">
         <v>10</v>
       </c>
-      <c r="C5" s="1">
+      <c r="D5" s="1">
         <v>150</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="1">
         <f>hanzi+wenben</f>
         <v>160</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" t="str">
-        <f>IF(D5&gt;100,"大于100","小于等于100")</f>
+      <c r="F5" s="1"/>
+      <c r="G5" t="str">
+        <f>IF(E5&gt;100,"大于100","小于等于100")</f>
         <v>大于100</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -567,75 +587,82 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1">
         <v>60</v>
       </c>
-      <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1">
         <v>70</v>
       </c>
-      <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="1"/>
+      <c r="C10" s="1">
         <v>50</v>
       </c>
-      <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1">
         <v>80</v>
       </c>
-      <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="3">
-        <f>SUM(B8:B11)</f>
+      <c r="B12" s="1"/>
+      <c r="C12" s="3">
+        <f>SUM(C8:C11)</f>
         <v>260</v>
       </c>
-      <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -643,8 +670,9 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -652,8 +680,9 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -661,8 +690,9 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -670,8 +700,9 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -679,8 +710,9 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -688,8 +720,9 @@
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -697,8 +730,9 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -706,8 +740,9 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -715,8 +750,9 @@
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -724,11 +760,12 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"你,我,她"</formula1>
     </dataValidation>
   </dataValidations>
@@ -738,7 +775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -799,7 +836,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:E12"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
@@ -825,7 +862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="E2:F11"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
